--- a/DSI Progress Log.xlsx
+++ b/DSI Progress Log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aiaqu\git_clones\DSI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97CB1D03-CCF6-4842-84B9-2AF564D6A742}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA99F574-6A30-478A-8C52-0EF95418B6D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-25710" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{1B1BEAF2-9B63-4AFB-A847-59D32D4FBDAB}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="17">
   <si>
     <t>Date</t>
   </si>
@@ -72,7 +72,10 @@
     <t>example problems</t>
   </si>
   <si>
-    <t>intro vids</t>
+    <t>first visualization</t>
+  </si>
+  <si>
+    <t>Filters and pages</t>
   </si>
 </sst>
 </file>
@@ -446,7 +449,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D71598C-6D19-4B31-A08E-42679BDBEEF1}">
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -454,7 +457,7 @@
     <col min="3" max="3" width="9.140625" style="3"/>
     <col min="4" max="4" width="16.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.85546875" customWidth="1"/>
+    <col min="6" max="6" width="16.28515625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10.28515625" customWidth="1"/>
     <col min="9" max="9" width="11.85546875" bestFit="1" customWidth="1"/>
@@ -591,7 +594,15 @@
         <v>20</v>
       </c>
       <c r="K8" s="4">
-        <v>0.11</v>
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>46170</v>
+      </c>
+      <c r="F9" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
